--- a/InputData/trans/EoNVFEwFC/Elast of New Veh Fuel Econ wrt Fuel Cost.xlsx
+++ b/InputData/trans/EoNVFEwFC/Elast of New Veh Fuel Econ wrt Fuel Cost.xlsx
@@ -2978,31 +2978,32 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010095990DC6317597479C114DD4E6AB1F33" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="00c0eb7d4c43453177323eb1ac58d7e7">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="7889d872-e2a2-4afb-87bc-97561eced75f" xmlns:ns3="c9df191c-55f2-496b-9838-9a5abe4742ad" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b5fe72540fcc493259a136614ad94e00" ns1:_="" ns2:_="" ns3:_="">
-    <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
-    <xsd:import namespace="7889d872-e2a2-4afb-87bc-97561eced75f"/>
-    <xsd:import namespace="c9df191c-55f2-496b-9838-9a5abe4742ad"/>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D257B2780BAD0A45A02FA065B9C6CC6A" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="54b727ac31dab95898e9cf92f0402afe">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cb176f07-3112-4ee9-93fd-ae2cb5f3e433" xmlns:ns3="6b15a3a4-8173-42d6-9deb-398ec38eca4b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="42611c3eb46fef4c2b2610d1e51cc1b0" ns2:_="" ns3:_="">
+    <xsd:import namespace="cb176f07-3112-4ee9-93fd-ae2cb5f3e433"/>
+    <xsd:import namespace="6b15a3a4-8173-42d6-9deb-398ec38eca4b"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element name="documentManagement">
             <xsd:complexType>
               <xsd:all>
-                <xsd:element ref="ns2:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns2:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns1:_ip_UnifiedCompliancePolicyProperties" minOccurs="0"/>
-                <xsd:element ref="ns1:_ip_UnifiedCompliancePolicyUIAction" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -3010,24 +3011,85 @@
       </xsd:complexType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="http://schemas.microsoft.com/sharepoint/v3" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="cb176f07-3112-4ee9-93fd-ae2cb5f3e433" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="_ip_UnifiedCompliancePolicyProperties" ma:index="18" nillable="true" ma:displayName="Unified Compliance Policy Properties" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyProperties">
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="_ip_UnifiedCompliancePolicyUIAction" ma:index="19" nillable="true" ma:displayName="Unified Compliance Policy UI Action" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyUIAction">
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="12" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="13" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="14" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="18" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="19" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="20" nillable="true" ma:displayName="Length (seconds)" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="22" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="ca0deac2-43b9-460d-a4eb-012f87ec990e" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="7889d872-e2a2-4afb-87bc-97561eced75f" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="6b15a3a4-8173-42d6-9deb-398ec38eca4b" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="8" nillable="true" ma:displayName="Shared With" ma:description="" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="10" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -3046,70 +3108,23 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="9" nillable="true" ma:displayName="Shared With Details" ma:description="" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="11" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
         </xsd:restriction>
       </xsd:simpleType>
     </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="c9df191c-55f2-496b-9838-9a5abe4742ad" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="10" nillable="true" ma:displayName="MediaServiceMetadata" ma:description="" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:description="" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="12" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="13" nillable="true" ma:displayName="MediaServiceAutoTags" ma:description="" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="14" nillable="true" ma:displayName="MediaServiceLocation" ma:description="" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="15" nillable="true" ma:displayName="MediaServiceOCR" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="17" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="20" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="21" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
+    <xsd:element name="TaxCatchAll" ma:index="23" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{caf201a3-c970-477d-b8ee-c5923cb026e5}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="6b15a3a4-8173-42d6-9deb-398ec38eca4b">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
     </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
@@ -3220,23 +3235,10 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09D7702E-16D9-4032-BF53-D3B5B6BD202F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{212F4B3A-6E19-43CC-906B-82F592F00D57}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A1BDA0E2-4F5A-4388-A0A9-28713DEC22B5}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{071CA728-021D-49CC-B015-0D75BFC4965B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F342BC8C-9E56-4DD7-B76F-DB595A5BC707}"/>
 </file>